--- a/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/02_WIM2 - Ön Analiz, Kaynak ve Çevreleme/EKG-KLT-MTR-02_garanti_olayi_ciddiyeti_ve_eskalasyon_matrisi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/02_WIM2 - Ön Analiz, Kaynak ve Çevreleme/EKG-KLT-MTR-02_garanti_olayi_ciddiyeti_ve_eskalasyon_matrisi.xlsx
@@ -850,7 +850,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-MTR-02&amp;C&amp;"Arial,Regular"&amp;11Garanti Olayı Ciddiyeti ve Eskalasyon Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 03.09.2026
+Revizyon nedeni: Süre varsayımları kaldırıldı; olay riski, görev ve onaylı müşteri/iç reaksiyon şartına bağlı matris kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1036,7 +1037,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-MTR-02&amp;C&amp;"Arial,Regular"&amp;11Garanti Olayı Ciddiyeti ve Eskalasyon Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 03.09.2026
+Revizyon nedeni: Süre varsayımları kaldırıldı; olay riski, görev ve onaylı müşteri/iç reaksiyon şartına bağlı matris kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>